--- a/artfynd/A 10200-2026 artfynd.xlsx
+++ b/artfynd/A 10200-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>94739236</v>
+        <v>94712060</v>
       </c>
       <c r="B2" t="n">
-        <v>56599</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100124</v>
+        <v>100065</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Backsvala</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Riparia riparia</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,34 +705,30 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>pulli</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grustag SO Persgård, Högryd, Sibbarp, Hl</t>
+          <t>Högryd 21,Varberg, Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>351228.1741480788</v>
+        <v>351208</v>
       </c>
       <c r="R2" t="n">
-        <v>6326052.144517433</v>
+        <v>6326027</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,27 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
+          <t>2021-07-06</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
+          <t>2021-07-06</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Kunde ses i två av de 17 bohålen.</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +782,488 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Silke Klick</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Silke Klick, Britta Svensson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>94573232</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57890</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100082</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Röd glada</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Milvus milvus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Högryd,Varberg, Hl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>351134</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6325970</v>
+      </c>
+      <c r="S3" t="n">
+        <v>8</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sibbarp</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2021-06-30</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2021-06-30</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Britta Svensson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Britta Svensson, Silke Klick</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>94739236</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58203</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100124</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Backsvala</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Riparia riparia</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>pulli</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Grustag SO Persgård, Högryd, Sibbarp, Hl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>351228</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6326053</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sibbarp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-07-07</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-07-07</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Kunde ses i två av de 17 bohålen.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Lars Eric Rahm</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Lars Eric Rahm, Magnus Rahm, Birger Kaiser</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>94573237</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58209</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102980</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ladusvala</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hirundo rustica</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Högryd,Varberg, Hl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>351134</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6325970</v>
+      </c>
+      <c r="S5" t="n">
+        <v>8</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sibbarp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-06-30</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-06-30</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Britta Svensson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Britta Svensson, Silke Klick</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>94573238</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58212</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102981</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Hussvala</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Delichon urbicum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Högryd,Varberg, Hl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>351134</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6325970</v>
+      </c>
+      <c r="S6" t="n">
+        <v>8</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sibbarp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-06-30</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-06-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Britta Svensson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Britta Svensson, Silke Klick</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
